--- a/artfynd/A 17733-2022 artfynd.xlsx
+++ b/artfynd/A 17733-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 17733-2022 artfynd.xlsx
+++ b/artfynd/A 17733-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>883427</v>
+        <v>883424</v>
       </c>
       <c r="B2" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -720,14 +715,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Öravattnet, Småmyrorna, Jmt</t>
+          <t>Öravattnet, SV Småmyrorna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>530573.8319821832</v>
+        <v>530528</v>
       </c>
       <c r="R2" t="n">
-        <v>7022845.654562884</v>
+        <v>7022839</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -757,19 +752,9 @@
           <t>2011-09-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2011-09-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1980735</v>
+        <v>883425</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -845,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530528.0109085409</v>
+        <v>530522</v>
       </c>
       <c r="R3" t="n">
-        <v>7022838.929107375</v>
+        <v>7022854</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -878,19 +858,9 @@
           <t>2011-09-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2011-09-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1980739</v>
+        <v>883426</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -962,14 +927,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Öravattnet, Småmyrorna, Jmt</t>
+          <t>Öravattnet, SV Småmyrorna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>530573.8319821832</v>
+        <v>530526</v>
       </c>
       <c r="R4" t="n">
-        <v>7022845.654562884</v>
+        <v>7022866</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -999,19 +964,9 @@
           <t>2011-09-27</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2011-09-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>883424</v>
+        <v>883427</v>
       </c>
       <c r="B5" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,14 +1033,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Öravattnet, SV Småmyrorna, Jmt</t>
+          <t>Öravattnet, Småmyrorna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>530528.0109085409</v>
+        <v>530574</v>
       </c>
       <c r="R5" t="n">
-        <v>7022838.929107375</v>
+        <v>7022846</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1120,19 +1070,9 @@
           <t>2011-09-27</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2011-09-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,6 +1096,748 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1906634</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80367</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6457</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dvärgtufs</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Scytinium teretiusculum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Öravattnet, SV Småmyrorna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>530526</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7022866</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2011-09-27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2011-09-27</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1980735</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Öravattnet, SV Småmyrorna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>530528</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7022839</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2011-09-27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2011-09-27</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1980736</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Öravattnet, SV Småmyrorna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>530522</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7022854</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2011-09-27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2011-09-27</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1980738</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Öravattnet, SV Småmyrorna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>530526</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7022866</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2011-09-27</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2011-09-27</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1980739</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Öravattnet, Småmyrorna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>530574</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7022846</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2011-09-27</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2011-09-27</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2067288</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Öravattnet, SV Småmyrorna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>530522</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7022854</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2011-09-27</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2011-09-27</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2067290</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Öravattnet, SV Småmyrorna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>530526</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7022866</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2011-09-27</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2011-09-27</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17733-2022 artfynd.xlsx
+++ b/artfynd/A 17733-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/883424</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/883425</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/883426</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/883427</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1906634</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1980735</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1980736</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,6 +1560,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1980738</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1626,6 +1671,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1980739</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,6 +1782,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2067288</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1838,8 +1893,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2067290</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>